--- a/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 32,76</t>
+          <t>-3,69; 34,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 31,06</t>
+          <t>0,32; 31,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 35,92</t>
+          <t>4,51; 36,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 22,88</t>
+          <t>-11,43; 23,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 33,36</t>
+          <t>-0,56; 29,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 32,34</t>
+          <t>2,74; 32,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 23,39</t>
+          <t>-1,33; 21,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 27,4</t>
+          <t>4,97; 27,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 29,49</t>
+          <t>8,58; 29,94</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 165,68</t>
+          <t>-13,37; 179,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 173,42</t>
+          <t>-0,09; 165,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 196,1</t>
+          <t>13,3; 203,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 91,22</t>
+          <t>-30,71; 91,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 135,26</t>
+          <t>-1,24; 125,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 139,28</t>
+          <t>7,14; 138,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 97,72</t>
+          <t>-4,26; 88,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,56; 119,38</t>
+          <t>14,37; 117,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,26; 127,17</t>
+          <t>23,91; 129,89</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 13,65</t>
+          <t>-12,91; 14,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 15,85</t>
+          <t>-9,88; 18,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,92; 60,31</t>
+          <t>35,83; 61,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 5,22</t>
+          <t>-22,77; 5,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,59; -2,16</t>
+          <t>-28,64; -2,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,68; 43,51</t>
+          <t>17,19; 45,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 5,59</t>
+          <t>-14,08; 6,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 3,04</t>
+          <t>-16,55; 3,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,62; 48,97</t>
+          <t>30,7; 50,05</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 46,96</t>
+          <t>-30,91; 50,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 52,86</t>
+          <t>-24,24; 65,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,44; 219,77</t>
+          <t>75,82; 229,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,32; 15,06</t>
+          <t>-43,29; 14,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,49; -6,96</t>
+          <t>-52,22; -2,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,21; 112,27</t>
+          <t>31,74; 121,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 15,41</t>
+          <t>-29,85; 17,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 8,66</t>
+          <t>-35,89; 9,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63,42; 139,82</t>
+          <t>65,55; 142,7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 26,42</t>
+          <t>-2,47; 26,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 16,42</t>
+          <t>-10,64; 16,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,11; 57,82</t>
+          <t>31,48; 57,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 17,38</t>
+          <t>-6,97; 18,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 15,98</t>
+          <t>-9,37; 14,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,5; 60,16</t>
+          <t>35,44; 60,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 19,46</t>
+          <t>-0,3; 19,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 12,22</t>
+          <t>-7,22; 12,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37,86; 55,19</t>
+          <t>38,33; 55,75</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 126,05</t>
+          <t>-8,43; 123,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 80,65</t>
+          <t>-31,82; 81,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,15; 310,72</t>
+          <t>89,79; 288,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 84,89</t>
+          <t>-22,2; 82,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 77,31</t>
+          <t>-30,83; 72,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109,55; 304,77</t>
+          <t>103,88; 297,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 85,33</t>
+          <t>-1,19; 86,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 55,93</t>
+          <t>-23,18; 53,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>117,36; 252,0</t>
+          <t>121,67; 262,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 19,19</t>
+          <t>-11,51; 19,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 20,16</t>
+          <t>-11,17; 18,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,13; 49,02</t>
+          <t>22,33; 49,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 10,4</t>
+          <t>-19,06; 9,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 8,9</t>
+          <t>-20,82; 9,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 34,24</t>
+          <t>-6,48; 35,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 8,76</t>
+          <t>-12,19; 9,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 9,65</t>
+          <t>-12,93; 9,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,7; 37,41</t>
+          <t>8,93; 37,51</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 63,94</t>
+          <t>-28,87; 64,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,73; 65,28</t>
+          <t>-26,55; 64,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,53; 168,11</t>
+          <t>51,85; 175,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 30,49</t>
+          <t>-41,97; 28,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 26,74</t>
+          <t>-44,5; 28,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 95,83</t>
+          <t>-13,34; 98,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 25,51</t>
+          <t>-27,43; 27,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 27,83</t>
+          <t>-30,42; 28,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,92; 109,03</t>
+          <t>22,18; 110,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 26,72</t>
+          <t>-37,38; 27,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-39,17; 18,81</t>
+          <t>-44,28; 16,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,69; 71,53</t>
+          <t>19,33; 70,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 30,98</t>
+          <t>-25,52; 28,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 35,12</t>
+          <t>-16,37; 35,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,95; 86,43</t>
+          <t>39,22; 86,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 21,37</t>
+          <t>-20,04; 22,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 19,02</t>
+          <t>-19,21; 19,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37,54; 75,26</t>
+          <t>38,05; 73,63</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,27; 95,21</t>
+          <t>-55,54; 98,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 77,94</t>
+          <t>-59,17; 55,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24,04; 325,14</t>
+          <t>24,84; 322,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-56,47; 406,51</t>
+          <t>-55,79; 320,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 460,56</t>
+          <t>-37,11; 518,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,87; 1365,55</t>
+          <t>72,93; 1348,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 90,73</t>
+          <t>-40,4; 107,07</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-36,78; 86,17</t>
+          <t>-36,66; 83,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>67,58; 370,17</t>
+          <t>69,9; 351,58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,28; 33,86</t>
+          <t>2,71; 33,22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,3; 35,61</t>
+          <t>0,6; 36,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30,49; 58,35</t>
+          <t>29,69; 57,37</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 19,66</t>
+          <t>-13,02; 19,01</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 18,07</t>
+          <t>-16,61; 20,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,32; 47,93</t>
+          <t>21,7; 49,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,16; 23,38</t>
+          <t>0,33; 22,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 21,64</t>
+          <t>-3,25; 21,21</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28,06; 49,04</t>
+          <t>29,91; 49,76</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10,13; 213,67</t>
+          <t>9,84; 218,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,1; 221,43</t>
+          <t>1,16; 231,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>95,49; 413,92</t>
+          <t>95,58; 383,92</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 70,64</t>
+          <t>-29,33; 65,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,34; 56,23</t>
+          <t>-42,44; 68,05</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45,47; 172,94</t>
+          <t>46,22; 179,68</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,07; 96,2</t>
+          <t>0,86; 89,85</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 86,55</t>
+          <t>-10,92; 83,56</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>82,3; 214,74</t>
+          <t>83,79; 207,32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 14,62</t>
+          <t>-6,96; 14,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 5,78</t>
+          <t>-13,53; 5,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43,22; 61,68</t>
+          <t>43,63; 60,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 11,01</t>
+          <t>-10,66; 10,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 2,89</t>
+          <t>-17,85; 2,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,77; 55,3</t>
+          <t>34,0; 55,07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 9,82</t>
+          <t>-4,76; 10,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 1,07</t>
+          <t>-13,19; 0,67</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>41,41; 55,35</t>
+          <t>41,53; 55,95</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 53,79</t>
+          <t>-19,08; 52,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 21,74</t>
+          <t>-37,3; 20,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>110,93; 244,08</t>
+          <t>112,27; 231,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 37,02</t>
+          <t>-25,01; 34,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 9,49</t>
+          <t>-42,86; 7,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>81,02; 185,63</t>
+          <t>85,25; 187,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 32,35</t>
+          <t>-13,3; 35,08</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,72; 3,77</t>
+          <t>-34,55; 2,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>108,12; 185,53</t>
+          <t>108,74; 189,49</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-26,0; -5,18</t>
+          <t>-26,67; -5,79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 2,15</t>
+          <t>-18,99; 1,73</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>37,62; 56,67</t>
+          <t>36,73; 55,77</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,5; -0,24</t>
+          <t>-20,77; -0,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 0,16</t>
+          <t>-18,9; 0,6</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>34,0; 53,57</t>
+          <t>35,1; 53,62</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-20,15; -5,08</t>
+          <t>-20,36; -5,47</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -1,57</t>
+          <t>-16,49; -1,95</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>37,97; 52,34</t>
+          <t>38,37; 51,9</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-57,77; -15,76</t>
+          <t>-56,84; -16,48</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 6,51</t>
+          <t>-41,67; 4,93</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>77,91; 176,7</t>
+          <t>72,82; 168,99</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-43,88; -0,62</t>
+          <t>-43,21; -0,21</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 0,46</t>
+          <t>-40,3; 1,99</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>68,87; 156,01</t>
+          <t>71,37; 153,41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-44,53; -13,38</t>
+          <t>-45,21; -15,24</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -4,78</t>
+          <t>-35,51; -4,97</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>82,17; 146,57</t>
+          <t>82,88; 145,11</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,52</t>
+          <t>-2,38; 7,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,68</t>
+          <t>-3,69; 5,89</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39,83; 49,82</t>
+          <t>40,01; 50,01</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 3,18</t>
+          <t>-7,06; 2,23</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,42</t>
+          <t>-9,02; 0,32</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>32,38; 42,66</t>
+          <t>33,1; 42,76</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,49</t>
+          <t>-3,6; 3,72</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,03</t>
+          <t>-5,18; 1,55</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>38,31; 44,87</t>
+          <t>37,91; 44,76</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 24,59</t>
+          <t>-7,02; 24,17</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 18,32</t>
+          <t>-10,68; 19,58</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>110,54; 165,8</t>
+          <t>110,29; 166,04</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 9,37</t>
+          <t>-17,82; 6,14</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 1,23</t>
+          <t>-22,12; 1,17</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>80,5; 122,86</t>
+          <t>83,62; 123,77</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 10,57</t>
+          <t>-9,66; 10,98</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 6,1</t>
+          <t>-14,18; 4,52</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>103,81; 134,42</t>
+          <t>101,06; 134,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 34,56</t>
+          <t>-2,42; 34,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 31,59</t>
+          <t>1,44; 31,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 36,3</t>
+          <t>4,41; 35,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 23,5</t>
+          <t>-10,72; 22,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 29,18</t>
+          <t>0,23; 29,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 32,03</t>
+          <t>2,84; 31,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 21,82</t>
+          <t>-1,1; 22,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 27,87</t>
+          <t>4,44; 26,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 29,94</t>
+          <t>7,93; 30,21</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 179,5</t>
+          <t>-9,55; 188,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 165,16</t>
+          <t>0,95; 171,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,3; 203,62</t>
+          <t>12,99; 191,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 91,02</t>
+          <t>-29,12; 95,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 125,82</t>
+          <t>0,64; 127,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 138,25</t>
+          <t>6,18; 128,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 88,78</t>
+          <t>-3,56; 94,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 117,57</t>
+          <t>13,15; 112,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,91; 129,89</t>
+          <t>21,78; 128,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 14,7</t>
+          <t>-14,41; 14,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 18,23</t>
+          <t>-11,23; 16,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,83; 61,94</t>
+          <t>36,01; 60,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 5,04</t>
+          <t>-25,25; 3,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,64; -2,13</t>
+          <t>-29,17; -3,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,19; 45,14</t>
+          <t>18,51; 44,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 6,2</t>
+          <t>-14,11; 6,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 3,44</t>
+          <t>-15,31; 2,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,7; 50,05</t>
+          <t>30,55; 49,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 50,36</t>
+          <t>-33,19; 47,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 65,44</t>
+          <t>-25,33; 57,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,82; 229,06</t>
+          <t>79,2; 215,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,29; 14,24</t>
+          <t>-47,54; 11,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -2,16</t>
+          <t>-53,79; -9,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,74; 121,34</t>
+          <t>35,07; 114,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 17,29</t>
+          <t>-31,39; 17,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 9,03</t>
+          <t>-32,54; 7,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,55; 142,7</t>
+          <t>65,88; 140,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 26,64</t>
+          <t>-2,48; 25,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 16,23</t>
+          <t>-11,57; 15,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,48; 57,29</t>
+          <t>31,46; 57,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 18,35</t>
+          <t>-6,1; 18,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 14,98</t>
+          <t>-9,79; 13,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,44; 60,01</t>
+          <t>35,44; 59,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 19,43</t>
+          <t>-1,58; 18,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 12,15</t>
+          <t>-6,82; 11,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,33; 55,75</t>
+          <t>38,15; 55,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 123,72</t>
+          <t>-7,9; 125,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,82; 81,11</t>
+          <t>-35,79; 76,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>89,79; 288,77</t>
+          <t>88,7; 287,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 82,67</t>
+          <t>-19,32; 93,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 72,94</t>
+          <t>-28,78; 64,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>103,88; 297,26</t>
+          <t>103,41; 289,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 86,6</t>
+          <t>-5,26; 76,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 53,79</t>
+          <t>-22,02; 48,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>121,67; 262,95</t>
+          <t>118,3; 248,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 19,37</t>
+          <t>-9,42; 20,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 18,8</t>
+          <t>-10,41; 19,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,33; 49,53</t>
+          <t>22,8; 49,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 9,69</t>
+          <t>-21,0; 9,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 9,07</t>
+          <t>-20,23; 10,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 35,36</t>
+          <t>-12,51; 34,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 9,62</t>
+          <t>-10,8; 10,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 9,83</t>
+          <t>-11,54; 9,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,93; 37,51</t>
+          <t>6,49; 36,33</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 64,45</t>
+          <t>-22,86; 68,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 64,57</t>
+          <t>-26,58; 64,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51,85; 175,8</t>
+          <t>51,57; 169,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 28,66</t>
+          <t>-44,8; 28,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 28,55</t>
+          <t>-44,42; 30,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 98,98</t>
+          <t>-19,87; 100,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 27,2</t>
+          <t>-25,86; 31,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 28,07</t>
+          <t>-27,38; 29,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,18; 110,52</t>
+          <t>17,81; 104,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-37,38; 27,73</t>
+          <t>-35,22; 32,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 16,38</t>
+          <t>-39,72; 20,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,33; 70,99</t>
+          <t>23,09; 76,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 28,99</t>
+          <t>-24,05; 29,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 35,97</t>
+          <t>-19,35; 35,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,22; 86,9</t>
+          <t>39,47; 87,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 22,65</t>
+          <t>-22,68; 21,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 19,21</t>
+          <t>-20,51; 20,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,05; 73,63</t>
+          <t>38,68; 74,12</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 98,66</t>
+          <t>-51,52; 125,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-59,17; 55,1</t>
+          <t>-56,28; 80,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24,84; 322,38</t>
+          <t>32,06; 344,29</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-55,79; 320,65</t>
+          <t>-59,32; 385,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 518,35</t>
+          <t>-39,61; 477,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,93; 1348,7</t>
+          <t>73,07; 1403,76</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 107,07</t>
+          <t>-44,4; 89,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 83,48</t>
+          <t>-37,86; 85,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>69,9; 351,58</t>
+          <t>67,63; 323,14</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,71; 33,22</t>
+          <t>2,07; 34,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,6; 36,8</t>
+          <t>1,43; 38,33</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29,69; 57,37</t>
+          <t>29,4; 59,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 19,01</t>
+          <t>-10,53; 20,47</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 20,03</t>
+          <t>-15,82; 18,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,7; 49,86</t>
+          <t>20,38; 48,46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,33; 22,07</t>
+          <t>-1,09; 21,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 21,21</t>
+          <t>-3,25; 21,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29,91; 49,76</t>
+          <t>28,73; 49,43</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9,84; 218,04</t>
+          <t>6,45; 235,14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1,16; 231,2</t>
+          <t>4,27; 245,51</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>95,58; 383,92</t>
+          <t>91,55; 413,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 65,47</t>
+          <t>-24,66; 70,56</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 68,05</t>
+          <t>-37,35; 58,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46,22; 179,68</t>
+          <t>45,4; 168,26</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,86; 89,85</t>
+          <t>-3,87; 84,53</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 83,56</t>
+          <t>-10,03; 83,52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>83,79; 207,32</t>
+          <t>81,11; 208,86</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 14,5</t>
+          <t>-6,97; 13,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 5,69</t>
+          <t>-14,14; 5,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43,63; 60,39</t>
+          <t>43,28; 61,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 10,66</t>
+          <t>-10,69; 10,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 2,32</t>
+          <t>-16,34; 2,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,0; 55,07</t>
+          <t>33,72; 55,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 10,75</t>
+          <t>-5,53; 8,92</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 0,67</t>
+          <t>-12,13; 1,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>41,53; 55,95</t>
+          <t>41,5; 55,75</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 52,2</t>
+          <t>-19,24; 49,74</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 20,97</t>
+          <t>-38,42; 21,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>112,27; 231,42</t>
+          <t>111,37; 234,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 34,72</t>
+          <t>-24,55; 31,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 7,32</t>
+          <t>-38,95; 9,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>85,25; 187,33</t>
+          <t>81,0; 181,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 35,08</t>
+          <t>-14,98; 28,76</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 2,2</t>
+          <t>-32,97; 3,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>108,74; 189,49</t>
+          <t>108,32; 190,9</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-26,67; -5,79</t>
+          <t>-25,45; -5,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 1,73</t>
+          <t>-18,54; 1,61</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>36,73; 55,77</t>
+          <t>36,2; 55,46</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,77; -0,12</t>
+          <t>-20,87; -0,69</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 0,6</t>
+          <t>-20,98; 0,64</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>35,1; 53,62</t>
+          <t>33,55; 53,08</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -5,47</t>
+          <t>-19,44; -5,37</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-16,49; -1,95</t>
+          <t>-16,75; -2,12</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>38,37; 51,9</t>
+          <t>38,81; 51,72</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-56,84; -16,48</t>
+          <t>-55,69; -14,81</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 4,93</t>
+          <t>-40,7; 5,06</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>72,82; 168,99</t>
+          <t>76,81; 166,05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-43,21; -0,21</t>
+          <t>-43,22; -0,81</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 1,99</t>
+          <t>-42,89; 1,97</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>71,37; 153,41</t>
+          <t>67,32; 153,42</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-45,21; -15,24</t>
+          <t>-44,36; -14,56</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-35,51; -4,97</t>
+          <t>-36,01; -5,34</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>82,88; 145,11</t>
+          <t>84,77; 143,35</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 7,34</t>
+          <t>-1,92; 7,84</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,89</t>
+          <t>-3,58; 6,17</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>40,01; 50,01</t>
+          <t>39,69; 49,51</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,23</t>
+          <t>-6,68; 2,96</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 0,32</t>
+          <t>-8,87; 0,61</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>33,1; 42,76</t>
+          <t>33,02; 42,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,72</t>
+          <t>-3,03; 3,71</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 1,55</t>
+          <t>-4,56; 1,92</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>37,91; 44,76</t>
+          <t>37,94; 44,93</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 24,17</t>
+          <t>-5,61; 25,77</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 19,58</t>
+          <t>-10,0; 19,76</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>110,29; 166,04</t>
+          <t>109,53; 163,0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 6,14</t>
+          <t>-17,07; 8,48</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 1,17</t>
+          <t>-22,54; 1,39</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>83,62; 123,77</t>
+          <t>83,66; 124,13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 10,98</t>
+          <t>-8,28; 10,99</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 4,52</t>
+          <t>-12,24; 5,8</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>101,06; 134,81</t>
+          <t>102,94; 136,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15,26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16,37</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>15,45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>16,38</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21,51</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,26</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,46</t>
+          <t>18,38</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,42</t>
+          <t>17,4</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 34,18</t>
+          <t>-11,06; 22,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 31,09</t>
+          <t>0,21; 33,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 35,5</t>
+          <t>2,04; 30,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 22,9</t>
+          <t>-2,63; 32,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 29,78</t>
+          <t>1,13; 31,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 31,88</t>
+          <t>4,2; 31,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 22,56</t>
+          <t>-1,0; 23,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 26,14</t>
+          <t>5,04; 27,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,93; 30,21</t>
+          <t>7,1; 26,61</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51,79%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>60,6%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>64,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,88%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>48,28%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 188,18</t>
+          <t>-28,2; 91,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 171,25</t>
+          <t>0,19; 135,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,99; 191,9</t>
+          <t>5,18; 130,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 95,04</t>
+          <t>-9,21; 165,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 127,12</t>
+          <t>4,23; 173,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 128,83</t>
+          <t>13,22; 181,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 94,63</t>
+          <t>-4,39; 97,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 112,43</t>
+          <t>14,56; 119,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,78; 128,28</t>
+          <t>21,13; 115,86</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-9,52</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-15,33</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32,34</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,29</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-9,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-15,33</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,04</t>
+          <t>42,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39,85</t>
+          <t>37,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 14,18</t>
+          <t>-23,56; 5,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 16,4</t>
+          <t>-27,59; -2,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,01; 60,57</t>
+          <t>19,29; 43,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 3,91</t>
+          <t>-14,07; 13,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,17; -3,65</t>
+          <t>-10,26; 15,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,51; 44,46</t>
+          <t>30,44; 54,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 6,03</t>
+          <t>-14,54; 5,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 2,68</t>
+          <t>-15,74; 3,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,55; 49,57</t>
+          <t>28,05; 45,89</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-20,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-33,03%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69,66%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>9,12%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>131,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-20,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-33,03%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>118,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 47,64</t>
+          <t>-45,32; 15,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 57,49</t>
+          <t>-53,49; -6,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,2; 215,06</t>
+          <t>36,03; 113,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,54; 11,06</t>
+          <t>-32,72; 46,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,79; -9,45</t>
+          <t>-24,59; 52,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,07; 114,29</t>
+          <t>68,49; 193,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 17,02</t>
+          <t>-32,51; 15,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 7,6</t>
+          <t>-34,74; 8,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,88; 140,44</t>
+          <t>59,85; 133,26</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,71</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>48,65</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>12,08</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,23</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>45,38</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,71</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,73</t>
+          <t>45,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47,17</t>
+          <t>46,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 25,96</t>
+          <t>-5,79; 17,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 15,97</t>
+          <t>-8,09; 15,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,46; 57,82</t>
+          <t>36,49; 59,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 18,41</t>
+          <t>-2,27; 26,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 13,99</t>
+          <t>-11,15; 16,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,44; 59,11</t>
+          <t>31,86; 57,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 18,25</t>
+          <t>-1,02; 19,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 11,14</t>
+          <t>-6,4; 12,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,15; 55,65</t>
+          <t>37,4; 54,95</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21,38%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>181,75%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>44,68%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>8,23%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167,89%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21,38%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>182,03%</t>
+          <t>167,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>175,37%</t>
+          <t>174,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 125,3</t>
+          <t>-19,4; 84,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 76,02</t>
+          <t>-25,51; 77,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88,7; 287,52</t>
+          <t>109,87; 304,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 93,06</t>
+          <t>-7,49; 126,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 64,16</t>
+          <t>-34,66; 80,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>103,41; 289,99</t>
+          <t>94,5; 313,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 76,14</t>
+          <t>-4,73; 85,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 48,43</t>
+          <t>-19,79; 55,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>118,3; 248,34</t>
+          <t>116,48; 251,23</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-5,2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,83</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19,28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,66</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,57</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>35,66</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-5,2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,83</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,82</t>
+          <t>36,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26,26</t>
+          <t>27,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 20,11</t>
+          <t>-19,61; 10,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 19,39</t>
+          <t>-21,82; 8,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,8; 49,74</t>
+          <t>-6,51; 35,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 9,45</t>
+          <t>-10,98; 19,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 10,26</t>
+          <t>-12,91; 20,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 34,52</t>
+          <t>21,31; 49,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 10,88</t>
+          <t>-12,35; 8,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 9,97</t>
+          <t>-11,38; 9,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 36,33</t>
+          <t>12,01; 38,22</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-12,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-14,31%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>47,29%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>12,83%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>9,83%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-12,75%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-14,31%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 68,17</t>
+          <t>-41,88; 30,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 64,44</t>
+          <t>-45,66; 26,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51,57; 169,55</t>
+          <t>-10,73; 101,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 28,68</t>
+          <t>-26,1; 63,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 30,85</t>
+          <t>-30,73; 65,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 100,76</t>
+          <t>48,33; 171,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 31,05</t>
+          <t>-27,33; 25,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 29,91</t>
+          <t>-26,34; 27,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,81; 104,29</t>
+          <t>30,49; 112,6</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11,67</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>69,06</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-3,6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-11,1</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>46,58</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11,67</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,82</t>
+          <t>46,78</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>57,61</t>
+          <t>58,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-35,22; 32,38</t>
+          <t>-24,76; 30,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 20,15</t>
+          <t>-15,23; 35,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23,09; 76,11</t>
+          <t>41,78; 88,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 29,6</t>
+          <t>-34,18; 26,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 35,58</t>
+          <t>-39,17; 18,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,47; 87,03</t>
+          <t>19,04; 71,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 21,11</t>
+          <t>-21,22; 21,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 20,08</t>
+          <t>-19,64; 19,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,68; 74,12</t>
+          <t>38,42; 76,1</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>44,24%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>261,76%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-7,12%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-21,92%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>44,24%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>253,27%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>153,9%</t>
+          <t>157,47%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,52; 125,39</t>
+          <t>-56,47; 406,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,28; 80,46</t>
+          <t>-33,27; 460,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32,06; 344,29</t>
+          <t>76,41; 1414,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 385,04</t>
+          <t>-52,27; 95,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 477,48</t>
+          <t>-56,73; 77,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,07; 1403,76</t>
+          <t>24,31; 329,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 89,39</t>
+          <t>-42,91; 90,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 85,79</t>
+          <t>-36,78; 86,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>67,63; 323,14</t>
+          <t>67,84; 376,2</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4,51</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,03</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>34,33</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>18,76</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>17,92</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>44,75</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4,51</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,84</t>
+          <t>43,75</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>39,59</t>
+          <t>38,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,07; 34,45</t>
+          <t>-10,77; 19,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,43; 38,33</t>
+          <t>-17,33; 18,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29,4; 59,08</t>
+          <t>19,47; 47,73</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 20,47</t>
+          <t>3,28; 33,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 18,37</t>
+          <t>0,3; 35,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,38; 48,46</t>
+          <t>29,16; 57,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 21,72</t>
+          <t>0,16; 23,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 21,92</t>
+          <t>-4,77; 21,64</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28,73; 49,43</t>
+          <t>27,18; 47,98</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>12,41%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-0,1%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>94,53%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>82,89%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>79,18%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>197,73%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>12,41%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-0,1%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>193,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>132,59%</t>
+          <t>129,67%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,45; 235,14</t>
+          <t>-23,9; 70,64</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4,27; 245,51</t>
+          <t>-42,34; 56,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>91,55; 413,35</t>
+          <t>43,75; 169,51</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 70,56</t>
+          <t>10,13; 213,67</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 58,36</t>
+          <t>0,1; 221,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45,4; 168,26</t>
+          <t>92,46; 409,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 84,53</t>
+          <t>1,07; 96,2</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 83,52</t>
+          <t>-13,5; 86,55</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>81,11; 208,86</t>
+          <t>78,49; 210,39</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,33</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-7,3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>48,16</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-4,66</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>52,49</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-7,3</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,86</t>
+          <t>51,72</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>49,04</t>
+          <t>49,97</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 13,72</t>
+          <t>-9,42; 11,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 5,64</t>
+          <t>-17,71; 2,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43,28; 61,51</t>
+          <t>38,82; 57,07</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 10,1</t>
+          <t>-6,55; 14,62</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 2,85</t>
+          <t>-15,2; 5,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,72; 55,03</t>
+          <t>42,23; 60,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 8,92</t>
+          <t>-5,14; 9,82</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 1,13</t>
+          <t>-13,2; 1,07</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>41,5; 55,75</t>
+          <t>43,38; 56,24</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-20,01%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>131,98%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>12,74%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-14,42%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>162,58%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-20,01%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>125,65%</t>
+          <t>160,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>142,58%</t>
+          <t>145,28%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 49,74</t>
+          <t>-22,71; 37,02</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 21,32</t>
+          <t>-42,44; 9,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>111,37; 234,53</t>
+          <t>88,56; 191,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 31,97</t>
+          <t>-17,95; 53,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-38,95; 9,76</t>
+          <t>-39,39; 21,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>81,0; 181,16</t>
+          <t>108,49; 241,72</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 28,76</t>
+          <t>-13,28; 32,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 3,88</t>
+          <t>-34,72; 3,77</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>108,32; 190,9</t>
+          <t>111,92; 187,85</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-10,26</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-9,22</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>44,11</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-15,67</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-8,58</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>46,87</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-10,26</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-9,22</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,03</t>
+          <t>47,16</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>45,36</t>
+          <t>45,56</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-25,45; -5,73</t>
+          <t>-20,5; -0,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 1,61</t>
+          <t>-20,12; 0,16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>36,2; 55,46</t>
+          <t>33,66; 53,67</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,87; -0,69</t>
+          <t>-26,0; -5,18</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 0,64</t>
+          <t>-19,0; 2,15</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>33,55; 53,08</t>
+          <t>37,9; 56,77</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-19,44; -5,37</t>
+          <t>-20,15; -5,08</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -2,12</t>
+          <t>-15,74; -1,57</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>38,81; 51,72</t>
+          <t>38,18; 52,74</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-24,58%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-22,09%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>105,66%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-38,85%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-21,29%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>116,21%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-24,58%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-22,09%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>105,47%</t>
+          <t>116,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>110,47%</t>
+          <t>110,95%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-55,69; -14,81</t>
+          <t>-43,88; -0,62</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-40,7; 5,06</t>
+          <t>-42,49; 0,46</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>76,81; 166,05</t>
+          <t>69,34; 155,89</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-43,22; -0,81</t>
+          <t>-57,77; -15,76</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 1,97</t>
+          <t>-41,09; 6,51</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>67,32; 153,42</t>
+          <t>78,25; 176,71</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-44,36; -14,56</t>
+          <t>-44,53; -13,38</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-36,01; -5,34</t>
+          <t>-35,04; -4,78</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>84,77; 143,35</t>
+          <t>82,53; 148,31</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-2,17</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-3,98</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>39,6</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>2,54</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>44,97</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-3,98</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>38,34</t>
+          <t>44,58</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>41,52</t>
+          <t>42,02</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 7,84</t>
+          <t>-6,71; 3,18</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 6,17</t>
+          <t>-8,87; 0,42</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39,69; 49,51</t>
+          <t>34,21; 43,88</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,96</t>
+          <t>-2,33; 7,52</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,61</t>
+          <t>-3,79; 5,68</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>33,02; 42,94</t>
+          <t>39,69; 49,01</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,71</t>
+          <t>-3,2; 3,49</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,92</t>
+          <t>-4,87; 2,03</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>37,94; 44,93</t>
+          <t>39,0; 45,16</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-5,83%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-10,66%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>106,14%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>7,72%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>136,65%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-5,83%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-10,66%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>102,76%</t>
+          <t>135,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>118,09%</t>
+          <t>119,51%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 25,77</t>
+          <t>-16,67; 9,37</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 19,76</t>
+          <t>-22,15; 1,23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>109,53; 163,0</t>
+          <t>84,68; 126,7</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 8,48</t>
+          <t>-6,75; 24,59</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 1,39</t>
+          <t>-10,76; 18,32</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>83,66; 124,13</t>
+          <t>110,17; 164,69</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 10,99</t>
+          <t>-8,62; 10,57</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 5,8</t>
+          <t>-13,37; 6,1</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>102,94; 136,72</t>
+          <t>104,99; 135,28</t>
         </is>
       </c>
     </row>
